--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingSummaryReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingSummaryReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lfey\source\repos\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91F34E9E-5AB4-42C4-8AAF-7C6E4AFD3D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A921B933-3C83-4EF9-864A-976AFFC534F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15900" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28910" yWindow="-20" windowWidth="29020" windowHeight="15700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>{{SelectedFilters}}</t>
   </si>
@@ -39,16 +39,10 @@
     <t>{{index+1}}</t>
   </si>
   <si>
-    <t>{{item.ActionDatetimeString}}</t>
-  </si>
-  <si>
     <t>Статус</t>
   </si>
   <si>
     <t>{{item.StateString}}</t>
-  </si>
-  <si>
-    <t>Дата</t>
   </si>
   <si>
     <t>Количество</t>
@@ -138,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -163,6 +157,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -494,13 +491,13 @@
     <col min="1021" max="1024" width="14.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1020" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1020" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="D1" s="6"/>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
@@ -512,7 +509,7 @@
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
+      <c r="D2" s="9"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
@@ -1533,16 +1530,14 @@
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AMB3" s="2"/>
+      <c r="AMA3" s="2"/>
+      <c r="AMB3"/>
       <c r="AMC3"/>
       <c r="AMD3"/>
       <c r="AME3"/>
@@ -1553,15 +1548,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="AMB4" s="2"/>
+      <c r="AMA4" s="2"/>
+      <c r="AMB4"/>
       <c r="AMC4"/>
       <c r="AMD4"/>
       <c r="AME4"/>
@@ -1570,8 +1563,8 @@
     <row r="5" spans="1:1020" ht="11.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingSummaryReport.xlsx
+++ b/Source/Libraries/Core/Business/Vodovoz.Reports/Reports/Client/BulkDebtMailingSummaryReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lfey\source\repos\Vodovoz\Source\Libraries\Core\Business\Vodovoz.Reports\Reports\Client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A921B933-3C83-4EF9-864A-976AFFC534F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9583874D-E9F1-48A2-B7D1-CD628A9ADCE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28910" yWindow="-20" windowWidth="29020" windowHeight="15700" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>{{SelectedFilters}}</t>
   </si>
@@ -52,6 +52,18 @@
   </si>
   <si>
     <t>Сводный отчет о рассылке писем о задолженности</t>
+  </si>
+  <si>
+    <t>Тип письма</t>
+  </si>
+  <si>
+    <t>{{item.EmailTypeString}}</t>
+  </si>
+  <si>
+    <t>Организация</t>
+  </si>
+  <si>
+    <t>{{item.OrganizationName}}</t>
   </si>
 </sst>
 </file>
@@ -132,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -156,10 +168,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -479,10 +488,10 @@
   <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17" style="1" customWidth="1"/>
-    <col min="5" max="5" width="94.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" style="1" customWidth="1"/>
     <col min="6" max="6" width="44.33203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="30.44140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="24.109375" style="1" customWidth="1"/>
@@ -497,8 +506,8 @@
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -509,8 +518,8 @@
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="1"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -1531,9 +1540,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="AMA3" s="2"/>
@@ -1548,9 +1563,15 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
       <c r="AMA4" s="2"/>
@@ -1563,8 +1584,8 @@
     <row r="5" spans="1:1020" ht="11.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
